--- a/backend/optimizacion_resultados.xlsx
+++ b/backend/optimizacion_resultados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,22 +445,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>124.4444</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>75.5556</v>
+        <v>1142.8572</v>
       </c>
     </row>
     <row r="4">
@@ -471,56 +471,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>142.2222</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>37.7778</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>88.88890000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>37.7778</v>
+        <v>714.2857</v>
       </c>
     </row>
   </sheetData>
